--- a/data/dataset_panne.xlsx
+++ b/data/dataset_panne.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F231"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7472,6 +7472,566 @@
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr"/>
     </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>neighborhood_outage</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>makan electricte fel houma</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>neighborhood_outage</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>ma kaynach electricite fel houma</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>neighborhood_outage</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>ma kaynach kahraba fel quartier</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>neighborhood_outage</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>toute la houma ma fiha ch kahraba</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>neighborhood_outage</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>l'electricite maqto3a fel houma</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>meter_problem</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>mon compteur clignote</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>meter_problem</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>mon compteur fait du bruit</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>meter_problem</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>compteur ta3i yclignoti</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>meter_problem</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>compteur ta3i ydir bruit</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>meter_problem</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>compteur ne fonctionne plus</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>report_breakdown</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>3andi panne</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>report_breakdown</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>kifach nsignali panne</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>report_breakdown</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>comment signaler une panne</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>report_breakdown</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>nheb nsigali panne</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>report_breakdown</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>kifach ndir bach nsigali panne</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>voltage_problem</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>el courant da3if bzaf</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>voltage_problem</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>le courant est très faible</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>voltage_problem</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>courant faible fel dar</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>voltage_problem</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>kahraba da3fa بزاف</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>PANNE</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>voltage_problem</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>la tension est faible chez moi</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>scenario_panne.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
